--- a/docs/CKDESK-FEATURES-BY-ROLE.xlsx
+++ b/docs/CKDESK-FEATURES-BY-ROLE.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3352" uniqueCount="520">
   <si>
     <t>Area</t>
   </si>
@@ -487,6 +487,18 @@
     <t>Act on many tickets at once (up to 500).</t>
   </si>
   <si>
+    <t>Auto-close after the reopen window</t>
+  </si>
+  <si>
+    <t>A resolved ticket closes by itself when nobody reopens it in time.</t>
+  </si>
+  <si>
+    <t>Auto close</t>
+  </si>
+  <si>
+    <t>Runs whenever someone opens the Home page (there is no scheduled job)</t>
+  </si>
+  <si>
     <t>Ticket history</t>
   </si>
   <si>
@@ -550,15 +562,30 @@
     <t>E-mail reply to request</t>
   </si>
   <si>
-    <t>OEM e-mail on AC and Genset tickets</t>
-  </si>
-  <si>
-    <t>A table-style mail goes to the store's OEM automatically; OEM replies show in the conversation.</t>
+    <t>AC ticket: automatic OEM e-mail and In Progress</t>
+  </si>
+  <si>
+    <t>The ticket is mailed to the store's AC OEM by itself (table-style mail) and moves to In Progress; OEM replies show in the conversation.</t>
   </si>
   <si>
     <t>Notify vendor</t>
   </si>
   <si>
+    <t>Works when the store has an AC OEM mapped; confirmed working on main</t>
+  </si>
+  <si>
+    <t>Genset ticket: automatic OEM e-mail and In Progress</t>
+  </si>
+  <si>
+    <t>The same automatic mail and In Progress for genset tickets.</t>
+  </si>
+  <si>
+    <t>Built - switched off</t>
+  </si>
+  <si>
+    <t>Code is on main but NOT switched on: needs the category set to Genset in Admin and a Genset OEM on each store (the Genset sheet will supply the addresses)</t>
+  </si>
+  <si>
     <t>Ticket e-mails</t>
   </si>
   <si>
@@ -589,12 +616,15 @@
     <t>Browser push notifications</t>
   </si>
   <si>
-    <t>Optional push messages in the browser (asks once).</t>
+    <t>Optional push messages in the browser.</t>
   </si>
   <si>
     <t>Mobile / push notifications</t>
   </si>
   <si>
+    <t>Code is on main but the live server has no push keys, so it is switched off</t>
+  </si>
+  <si>
     <t>Mailbox settings</t>
   </si>
   <si>
@@ -712,6 +742,9 @@
     <t>Technician, Requester</t>
   </si>
   <si>
+    <t>Works once each store has its CVM assigned in Admin (set-up in progress)</t>
+  </si>
+  <si>
     <t>Business Rules</t>
   </si>
   <si>
@@ -1216,10 +1249,10 @@
     <t>12 fixed Excel-style reports plus weekly, monthly, priority-wise and repeated AC complaint reports; search by name.</t>
   </si>
   <si>
-    <t>Scheduled reports and exports</t>
-  </si>
-  <si>
-    <t>CSV and Excel exports; scheduled daily, weekly or monthly reports to company addresses.</t>
+    <t>Excel and CSV exports</t>
+  </si>
+  <si>
+    <t>Download a report or a list as CSV or Excel; every export is logged.</t>
   </si>
   <si>
     <t>India-time reporting</t>
@@ -1285,9 +1318,6 @@
     <t>Mails are classified (rules, optional AI) and a reviewer turns them into tickets.</t>
   </si>
   <si>
-    <t>Built - switched off</t>
-  </si>
-  <si>
     <t>E-mail commands / mail fetching</t>
   </si>
   <si>
@@ -1354,10 +1384,16 @@
     <t>A scheduled task at 08:00 that saves the day's highest and lowest temperature of each city.</t>
   </si>
   <si>
+    <t>Send scheduled reports by e-mail</t>
+  </si>
+  <si>
+    <t>The screens to define a schedule exist, but no job sends the reports yet.</t>
+  </si>
+  <si>
     <t>Reminder for a waiting quote</t>
   </si>
   <si>
-    <t>Remind the approver after 1 day and the vendor after 2 days.</t>
+    <t>Remind the approver after 1 day and the vendor after 2 days if a revised price is not answered.</t>
   </si>
   <si>
     <t>Vendor replies by e-mail</t>
@@ -2065,13 +2101,13 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2">
         <v>2</v>
@@ -2085,19 +2121,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2385,7 +2421,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -2394,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="2">
         <v>0</v>
@@ -2405,19 +2441,19 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C21" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3">
         <v>99</v>
       </c>
       <c r="E21" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F21" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -2438,7 +2474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -3455,36 +3491,36 @@
         <v>8</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>158</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>65</v>
+      <c r="D40" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>40</v>
@@ -3492,10 +3528,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>37</v>
@@ -3507,10 +3543,10 @@
         <v>8</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>40</v>
@@ -3518,25 +3554,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G42" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>40</v>
@@ -3559,10 +3595,10 @@
         <v>9</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>40</v>
@@ -3570,10 +3606,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>37</v>
@@ -3585,10 +3621,10 @@
         <v>9</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>40</v>
@@ -3596,10 +3632,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>37</v>
@@ -3611,10 +3647,10 @@
         <v>9</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>40</v>
@@ -3622,10 +3658,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>37</v>
@@ -3637,10 +3673,10 @@
         <v>9</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>40</v>
@@ -3648,10 +3684,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>37</v>
@@ -3663,47 +3699,47 @@
         <v>9</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>37</v>
+      <c r="D48" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>183</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>40</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>37</v>
@@ -3715,10 +3751,10 @@
         <v>9</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>40</v>
@@ -3726,10 +3762,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>37</v>
@@ -3741,10 +3777,10 @@
         <v>9</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>40</v>
@@ -3752,10 +3788,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>37</v>
@@ -3767,10 +3803,10 @@
         <v>9</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>40</v>
@@ -3778,36 +3814,36 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>37</v>
+      <c r="D52" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>37</v>
@@ -3816,13 +3852,13 @@
         <v>37</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>40</v>
@@ -3830,10 +3866,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>37</v>
@@ -3845,10 +3881,10 @@
         <v>10</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>40</v>
@@ -3856,10 +3892,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>37</v>
@@ -3871,10 +3907,10 @@
         <v>10</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>40</v>
@@ -3882,10 +3918,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>37</v>
@@ -3897,10 +3933,10 @@
         <v>10</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>40</v>
@@ -3908,10 +3944,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>37</v>
@@ -3923,10 +3959,10 @@
         <v>10</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>40</v>
@@ -3934,10 +3970,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>37</v>
@@ -3946,13 +3982,13 @@
         <v>37</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>40</v>
@@ -3960,10 +3996,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>37</v>
@@ -3972,13 +4008,13 @@
         <v>37</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>40</v>
@@ -3986,10 +4022,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>37</v>
@@ -4012,10 +4048,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>37</v>
@@ -4027,10 +4063,10 @@
         <v>11</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>40</v>
@@ -4038,10 +4074,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>37</v>
@@ -4053,10 +4089,10 @@
         <v>11</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="H62" s="5" t="s">
         <v>40</v>
@@ -4064,10 +4100,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>37</v>
@@ -4079,10 +4115,10 @@
         <v>11</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>227</v>
+        <v>11</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>40</v>
@@ -4090,10 +4126,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>37</v>
@@ -4105,10 +4141,10 @@
         <v>11</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>230</v>
+        <v>52</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>161</v>
+        <v>234</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>40</v>
@@ -4116,10 +4152,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>37</v>
@@ -4128,13 +4164,13 @@
         <v>37</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>40</v>
@@ -4142,10 +4178,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>37</v>
@@ -4154,24 +4190,24 @@
         <v>37</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>37</v>
@@ -4186,7 +4222,7 @@
         <v>52</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>40</v>
@@ -4194,16 +4230,16 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>65</v>
+      <c r="D68" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>12</v>
@@ -4212,7 +4248,7 @@
         <v>52</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>40</v>
@@ -4220,10 +4256,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>37</v>
@@ -4232,13 +4268,13 @@
         <v>37</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>40</v>
@@ -4246,25 +4282,25 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>37</v>
+      <c r="D70" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>40</v>
@@ -4272,10 +4308,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>37</v>
@@ -4287,10 +4323,10 @@
         <v>13</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>40</v>
@@ -4298,25 +4334,25 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>65</v>
+      <c r="D72" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="H72" s="5" t="s">
         <v>40</v>
@@ -4324,25 +4360,25 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D73" s="7" t="s">
-        <v>65</v>
+      <c r="D73" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="H73" s="5" t="s">
         <v>40</v>
@@ -4350,25 +4386,25 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>37</v>
+      <c r="D74" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>40</v>
@@ -4376,25 +4412,25 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D75" s="6" t="s">
-        <v>37</v>
+      <c r="D75" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>40</v>
@@ -4402,10 +4438,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>37</v>
@@ -4420,7 +4456,7 @@
         <v>52</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H76" s="5" t="s">
         <v>40</v>
@@ -4428,16 +4464,16 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>65</v>
+      <c r="D77" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>14</v>
@@ -4446,7 +4482,7 @@
         <v>52</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>40</v>
@@ -4454,16 +4490,16 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D78" s="7" t="s">
-        <v>65</v>
+      <c r="D78" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>14</v>
@@ -4472,7 +4508,7 @@
         <v>52</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="H78" s="5" t="s">
         <v>40</v>
@@ -4480,10 +4516,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>37</v>
@@ -4498,7 +4534,7 @@
         <v>52</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>161</v>
+        <v>275</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>40</v>
@@ -4506,10 +4542,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>37</v>
@@ -4518,13 +4554,13 @@
         <v>65</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>272</v>
+        <v>52</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>40</v>
@@ -4532,10 +4568,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>37</v>
@@ -4544,13 +4580,13 @@
         <v>65</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>272</v>
+        <v>52</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>40</v>
@@ -4558,10 +4594,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>37</v>
@@ -4573,10 +4609,10 @@
         <v>15</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>161</v>
+        <v>284</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>40</v>
@@ -4584,10 +4620,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>37</v>
@@ -4599,10 +4635,10 @@
         <v>15</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>280</v>
+        <v>165</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>40</v>
@@ -4610,10 +4646,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>37</v>
@@ -4628,7 +4664,7 @@
         <v>283</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>40</v>
@@ -4636,10 +4672,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>37</v>
@@ -4654,7 +4690,7 @@
         <v>283</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>40</v>
@@ -4662,10 +4698,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>37</v>
@@ -4677,10 +4713,10 @@
         <v>15</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>40</v>
@@ -4688,10 +4724,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>37</v>
@@ -4703,10 +4739,10 @@
         <v>15</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H87" s="5" t="s">
         <v>40</v>
@@ -4714,10 +4750,10 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>37</v>
@@ -4729,10 +4765,10 @@
         <v>15</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>40</v>
@@ -4740,10 +4776,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>37</v>
@@ -4755,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>161</v>
+        <v>304</v>
       </c>
       <c r="H89" s="5" t="s">
         <v>40</v>
@@ -4766,10 +4802,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>37</v>
@@ -4781,10 +4817,10 @@
         <v>15</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>182</v>
+        <v>308</v>
       </c>
       <c r="H90" s="5" t="s">
         <v>40</v>
@@ -4792,10 +4828,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>37</v>
@@ -4807,10 +4843,10 @@
         <v>15</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H91" s="5" t="s">
         <v>40</v>
@@ -4818,10 +4854,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>37</v>
@@ -4833,10 +4869,10 @@
         <v>15</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>40</v>
@@ -4844,10 +4880,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>37</v>
@@ -4856,13 +4892,13 @@
         <v>65</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>308</v>
+        <v>165</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>40</v>
@@ -4870,10 +4906,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>37</v>
@@ -4882,13 +4918,13 @@
         <v>65</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>311</v>
+        <v>50</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>40</v>
@@ -4896,10 +4932,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>37</v>
@@ -4914,7 +4950,7 @@
         <v>52</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>40</v>
@@ -4922,10 +4958,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>37</v>
@@ -4937,10 +4973,10 @@
         <v>16</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>40</v>
@@ -4948,10 +4984,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>37</v>
@@ -4966,7 +5002,7 @@
         <v>52</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>40</v>
@@ -4974,25 +5010,25 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D98" s="6" t="s">
-        <v>37</v>
+      <c r="D98" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>40</v>
@@ -5000,25 +5036,25 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="6" t="s">
-        <v>37</v>
+      <c r="D99" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>40</v>
@@ -5026,10 +5062,10 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>37</v>
@@ -5041,10 +5077,10 @@
         <v>17</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>40</v>
@@ -5052,10 +5088,10 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>37</v>
@@ -5067,10 +5103,10 @@
         <v>17</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>40</v>
@@ -5078,10 +5114,10 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>37</v>
@@ -5096,7 +5132,7 @@
         <v>61</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H102" s="5" t="s">
         <v>40</v>
@@ -5104,10 +5140,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>37</v>
@@ -5122,7 +5158,7 @@
         <v>61</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>40</v>
@@ -5130,10 +5166,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>37</v>
@@ -5148,7 +5184,7 @@
         <v>61</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>161</v>
+        <v>346</v>
       </c>
       <c r="H104" s="5" t="s">
         <v>40</v>
@@ -5156,10 +5192,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>37</v>
@@ -5171,10 +5207,10 @@
         <v>17</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>161</v>
+        <v>349</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>40</v>
@@ -5182,10 +5218,10 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>37</v>
@@ -5197,10 +5233,10 @@
         <v>17</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>345</v>
+        <v>165</v>
       </c>
       <c r="H106" s="5" t="s">
         <v>40</v>
@@ -5208,10 +5244,10 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>37</v>
@@ -5226,7 +5262,7 @@
         <v>52</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>348</v>
+        <v>165</v>
       </c>
       <c r="H107" s="5" t="s">
         <v>40</v>
@@ -5234,10 +5270,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>37</v>
@@ -5249,10 +5285,10 @@
         <v>17</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>40</v>
@@ -5260,10 +5296,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>37</v>
@@ -5275,10 +5311,10 @@
         <v>17</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>40</v>
@@ -5286,10 +5322,10 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>37</v>
@@ -5304,7 +5340,7 @@
         <v>61</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>40</v>
@@ -5312,10 +5348,10 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>37</v>
@@ -5330,7 +5366,7 @@
         <v>61</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>40</v>
@@ -5338,16 +5374,16 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D112" s="7" t="s">
-        <v>65</v>
+      <c r="D112" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E112" s="5" t="s">
         <v>17</v>
@@ -5356,7 +5392,7 @@
         <v>61</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>40</v>
@@ -5364,25 +5400,25 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>65</v>
+      <c r="D113" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>40</v>
@@ -5390,10 +5426,10 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>37</v>
@@ -5402,13 +5438,13 @@
         <v>65</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>161</v>
+        <v>346</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>40</v>
@@ -5416,10 +5452,10 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>37</v>
@@ -5431,10 +5467,10 @@
         <v>18</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>161</v>
+        <v>376</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>40</v>
@@ -5442,10 +5478,10 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>37</v>
@@ -5457,10 +5493,10 @@
         <v>18</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>373</v>
+        <v>165</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>40</v>
@@ -5468,10 +5504,10 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>37</v>
@@ -5483,10 +5519,10 @@
         <v>18</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>61</v>
+        <v>381</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>376</v>
+        <v>165</v>
       </c>
       <c r="H117" s="5" t="s">
         <v>40</v>
@@ -5494,10 +5530,10 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>37</v>
@@ -5509,10 +5545,10 @@
         <v>18</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>61</v>
+        <v>381</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>40</v>
@@ -5520,10 +5556,10 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>37</v>
@@ -5538,7 +5574,7 @@
         <v>61</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>40</v>
@@ -5546,10 +5582,10 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>37</v>
@@ -5561,10 +5597,10 @@
         <v>18</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="H120" s="5" t="s">
         <v>40</v>
@@ -5572,10 +5608,10 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>37</v>
@@ -5587,10 +5623,10 @@
         <v>18</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>161</v>
+        <v>340</v>
       </c>
       <c r="H121" s="5" t="s">
         <v>40</v>
@@ -5598,10 +5634,10 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>37</v>
@@ -5613,10 +5649,10 @@
         <v>18</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>61</v>
+        <v>381</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>161</v>
+        <v>343</v>
       </c>
       <c r="H122" s="5" t="s">
         <v>40</v>
@@ -5624,25 +5660,25 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D123" s="6" t="s">
-        <v>37</v>
+      <c r="D123" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>390</v>
+        <v>165</v>
       </c>
       <c r="H123" s="5" t="s">
         <v>40</v>
@@ -5650,25 +5686,25 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D124" s="6" t="s">
-        <v>37</v>
+      <c r="D124" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>393</v>
+        <v>165</v>
       </c>
       <c r="H124" s="5" t="s">
         <v>40</v>
@@ -5676,10 +5712,10 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>37</v>
@@ -5694,7 +5730,7 @@
         <v>61</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H125" s="5" t="s">
         <v>40</v>
@@ -5702,10 +5738,10 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>37</v>
@@ -5720,7 +5756,7 @@
         <v>61</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="H126" s="5" t="s">
         <v>40</v>
@@ -5728,10 +5764,10 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>37</v>
@@ -5743,10 +5779,10 @@
         <v>19</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>212</v>
+        <v>407</v>
       </c>
       <c r="H127" s="5" t="s">
         <v>40</v>
@@ -5754,10 +5790,10 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>37</v>
@@ -5772,7 +5808,7 @@
         <v>61</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H128" s="5" t="s">
         <v>40</v>
@@ -5780,10 +5816,10 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>37</v>
@@ -5792,13 +5828,13 @@
         <v>37</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>406</v>
+        <v>365</v>
       </c>
       <c r="H129" s="5" t="s">
         <v>40</v>
@@ -5806,10 +5842,10 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>37</v>
@@ -5818,13 +5854,13 @@
         <v>37</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="H130" s="5" t="s">
         <v>40</v>
@@ -5832,10 +5868,10 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>37</v>
@@ -5847,10 +5883,10 @@
         <v>20</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>48</v>
+        <v>381</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H131" s="5" t="s">
         <v>40</v>
@@ -5858,10 +5894,10 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>37</v>
@@ -5873,10 +5909,10 @@
         <v>20</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>52</v>
+        <v>381</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>161</v>
+        <v>418</v>
       </c>
       <c r="H132" s="5" t="s">
         <v>40</v>
@@ -5884,10 +5920,10 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>37</v>
@@ -5896,13 +5932,13 @@
         <v>37</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="H133" s="5" t="s">
         <v>40</v>
@@ -5910,10 +5946,10 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>37</v>
@@ -5922,13 +5958,13 @@
         <v>37</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>419</v>
+        <v>165</v>
       </c>
       <c r="H134" s="5" t="s">
         <v>40</v>
@@ -5936,114 +5972,114 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D135" s="8" t="s">
-        <v>422</v>
+      <c r="D135" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>424</v>
+        <v>40</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D136" s="8" t="s">
-        <v>422</v>
+      <c r="D136" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>428</v>
+        <v>40</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D137" s="6" t="s">
-        <v>37</v>
+      <c r="D137" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>40</v>
+        <v>434</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D138" s="6" t="s">
-        <v>37</v>
+      <c r="D138" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>40</v>
+        <v>438</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>37</v>
@@ -6058,7 +6094,7 @@
         <v>52</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="H139" s="5" t="s">
         <v>40</v>
@@ -6066,10 +6102,10 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>37</v>
@@ -6084,7 +6120,7 @@
         <v>52</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H140" s="5" t="s">
         <v>40</v>
@@ -6092,10 +6128,10 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>37</v>
@@ -6110,7 +6146,7 @@
         <v>52</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="H141" s="5" t="s">
         <v>40</v>
@@ -6118,16 +6154,16 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D142" s="7" t="s">
-        <v>65</v>
+      <c r="D142" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>23</v>
@@ -6136,7 +6172,7 @@
         <v>52</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>161</v>
+        <v>449</v>
       </c>
       <c r="H142" s="5" t="s">
         <v>40</v>
@@ -6144,25 +6180,25 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>65</v>
+        <v>451</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>209</v>
+        <v>452</v>
       </c>
       <c r="H143" s="5" t="s">
         <v>40</v>
@@ -6170,25 +6206,25 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>65</v>
+        <v>454</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>272</v>
+        <v>52</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="H144" s="5" t="s">
         <v>40</v>
@@ -6196,10 +6232,10 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>65</v>
@@ -6214,7 +6250,7 @@
         <v>52</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="H145" s="5" t="s">
         <v>40</v>
@@ -6222,10 +6258,10 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C146" s="7" t="s">
         <v>65</v>
@@ -6237,10 +6273,10 @@
         <v>24</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="H146" s="5" t="s">
         <v>40</v>
@@ -6248,10 +6284,10 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>65</v>
@@ -6263,10 +6299,10 @@
         <v>24</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>70</v>
+        <v>283</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>455</v>
+        <v>180</v>
       </c>
       <c r="H147" s="5" t="s">
         <v>40</v>
@@ -6274,10 +6310,10 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C148" s="7" t="s">
         <v>65</v>
@@ -6292,9 +6328,87 @@
         <v>52</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>458</v>
+        <v>165</v>
       </c>
       <c r="H148" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H151" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -6815,10 +6929,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>37</v>
@@ -6833,7 +6947,7 @@
         <v>70</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>40</v>
@@ -6841,10 +6955,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>37</v>
@@ -6856,10 +6970,10 @@
         <v>9</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>40</v>
@@ -6867,10 +6981,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>37</v>
@@ -6885,7 +6999,7 @@
         <v>70</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>40</v>
@@ -6893,10 +7007,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>37</v>
@@ -6911,7 +7025,7 @@
         <v>70</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>40</v>
@@ -6919,10 +7033,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>37</v>
@@ -6934,10 +7048,10 @@
         <v>9</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>40</v>
@@ -6945,10 +7059,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>37</v>
@@ -6963,7 +7077,7 @@
         <v>38</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>40</v>
@@ -6971,16 +7085,16 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>37</v>
+      <c r="D26" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>9</v>
@@ -6989,18 +7103,18 @@
         <v>38</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>37</v>
@@ -7015,7 +7129,7 @@
         <v>48</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>40</v>
@@ -7023,10 +7137,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>37</v>
@@ -7038,21 +7152,21 @@
         <v>11</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>37</v>
@@ -7064,10 +7178,10 @@
         <v>15</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>40</v>
@@ -7075,10 +7189,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>37</v>
@@ -7090,10 +7204,10 @@
         <v>15</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>40</v>
@@ -7101,10 +7215,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>37</v>
@@ -7119,7 +7233,7 @@
         <v>48</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>40</v>
@@ -7127,10 +7241,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>37</v>
@@ -7145,7 +7259,7 @@
         <v>48</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>40</v>
@@ -7153,10 +7267,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>37</v>
@@ -7168,10 +7282,10 @@
         <v>18</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>40</v>
@@ -7179,10 +7293,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>37</v>
@@ -7194,10 +7308,10 @@
         <v>18</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>40</v>
@@ -7205,10 +7319,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>37</v>
@@ -7220,10 +7334,10 @@
         <v>18</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>40</v>
@@ -7231,10 +7345,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>37</v>
@@ -7246,10 +7360,10 @@
         <v>20</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>40</v>
@@ -7257,10 +7371,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>37</v>
@@ -7272,10 +7386,10 @@
         <v>20</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>40</v>
@@ -7283,10 +7397,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>37</v>
@@ -7301,7 +7415,7 @@
         <v>48</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>40</v>
@@ -7309,10 +7423,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>37</v>
@@ -7327,7 +7441,7 @@
         <v>94</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>40</v>
@@ -7335,10 +7449,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>65</v>
@@ -7353,7 +7467,7 @@
         <v>70</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>40</v>
@@ -7368,7 +7482,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -8021,36 +8135,36 @@
         <v>8</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>158</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>65</v>
+      <c r="D26" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>40</v>
@@ -8058,10 +8172,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>37</v>
@@ -8073,10 +8187,10 @@
         <v>8</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>40</v>
@@ -8084,25 +8198,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>40</v>
@@ -8125,10 +8239,10 @@
         <v>9</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>40</v>
@@ -8136,10 +8250,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>37</v>
@@ -8151,10 +8265,10 @@
         <v>9</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>40</v>
@@ -8162,10 +8276,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>37</v>
@@ -8177,10 +8291,10 @@
         <v>9</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>40</v>
@@ -8188,10 +8302,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>37</v>
@@ -8203,10 +8317,10 @@
         <v>9</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>40</v>
@@ -8214,10 +8328,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>37</v>
@@ -8229,47 +8343,47 @@
         <v>9</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>37</v>
+      <c r="D34" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>183</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>40</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>37</v>
@@ -8281,10 +8395,10 @@
         <v>9</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>40</v>
@@ -8292,10 +8406,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>37</v>
@@ -8307,10 +8421,10 @@
         <v>9</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>40</v>
@@ -8318,10 +8432,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>37</v>
@@ -8330,13 +8444,13 @@
         <v>37</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>40</v>
@@ -8344,51 +8458,51 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>37</v>
+      <c r="D38" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>40</v>
@@ -8396,25 +8510,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>40</v>
@@ -8422,10 +8536,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>37</v>
@@ -8448,10 +8562,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>37</v>
@@ -8463,10 +8577,10 @@
         <v>11</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>40</v>
@@ -8489,10 +8603,10 @@
         <v>11</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>230</v>
+        <v>61</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>161</v>
+        <v>11</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>40</v>
@@ -8500,10 +8614,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>37</v>
@@ -8512,13 +8626,13 @@
         <v>37</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>40</v>
@@ -8526,10 +8640,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>37</v>
@@ -8538,39 +8652,39 @@
         <v>37</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>61</v>
+        <v>240</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>248</v>
+        <v>165</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>65</v>
+      <c r="D46" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>40</v>
@@ -8578,10 +8692,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>321</v>
+        <v>257</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>322</v>
+        <v>258</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>37</v>
@@ -8590,13 +8704,13 @@
         <v>37</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>40</v>
@@ -8604,25 +8718,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>324</v>
+        <v>260</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>325</v>
+        <v>261</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>37</v>
+      <c r="D48" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>326</v>
+        <v>183</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>40</v>
@@ -8630,10 +8744,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>37</v>
@@ -8645,10 +8759,10 @@
         <v>17</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>40</v>
@@ -8656,10 +8770,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>37</v>
@@ -8671,10 +8785,10 @@
         <v>17</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>40</v>
@@ -8682,10 +8796,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>37</v>
@@ -8700,7 +8814,7 @@
         <v>61</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>40</v>
@@ -8708,10 +8822,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>37</v>
@@ -8726,7 +8840,7 @@
         <v>61</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>40</v>
@@ -8734,10 +8848,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>37</v>
@@ -8752,7 +8866,7 @@
         <v>61</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>161</v>
+        <v>346</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>40</v>
@@ -8760,10 +8874,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>37</v>
@@ -8778,7 +8892,7 @@
         <v>61</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>40</v>
@@ -8786,10 +8900,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>37</v>
@@ -8804,7 +8918,7 @@
         <v>61</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>354</v>
+        <v>165</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>40</v>
@@ -8812,10 +8926,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>37</v>
@@ -8830,7 +8944,7 @@
         <v>61</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>40</v>
@@ -8838,10 +8952,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>37</v>
@@ -8856,7 +8970,7 @@
         <v>61</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>40</v>
@@ -8864,16 +8978,16 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>65</v>
+      <c r="D58" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>17</v>
@@ -8882,7 +8996,7 @@
         <v>61</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>40</v>
@@ -8890,25 +9004,25 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>65</v>
+      <c r="D59" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>40</v>
@@ -8916,10 +9030,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>37</v>
@@ -8928,13 +9042,13 @@
         <v>65</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>161</v>
+        <v>346</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>40</v>
@@ -8942,10 +9056,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>37</v>
@@ -8957,10 +9071,10 @@
         <v>18</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>161</v>
+        <v>376</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>40</v>
@@ -8968,10 +9082,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>37</v>
@@ -8983,10 +9097,10 @@
         <v>18</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>373</v>
+        <v>165</v>
       </c>
       <c r="H62" s="5" t="s">
         <v>40</v>
@@ -8994,10 +9108,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>37</v>
@@ -9009,10 +9123,10 @@
         <v>18</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>61</v>
+        <v>381</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>376</v>
+        <v>165</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>40</v>
@@ -9020,10 +9134,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>37</v>
@@ -9035,10 +9149,10 @@
         <v>18</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>61</v>
+        <v>381</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>40</v>
@@ -9046,10 +9160,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>37</v>
@@ -9064,7 +9178,7 @@
         <v>61</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>40</v>
@@ -9072,10 +9186,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>37</v>
@@ -9087,10 +9201,10 @@
         <v>18</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>40</v>
@@ -9098,10 +9212,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>37</v>
@@ -9116,7 +9230,7 @@
         <v>61</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>161</v>
+        <v>340</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>40</v>
@@ -9124,25 +9238,25 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>37</v>
+      <c r="D68" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>61</v>
+        <v>381</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>390</v>
+        <v>343</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>40</v>
@@ -9150,25 +9264,25 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>37</v>
+      <c r="D69" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>393</v>
+        <v>165</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>40</v>
@@ -9176,10 +9290,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>37</v>
@@ -9194,7 +9308,7 @@
         <v>61</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>40</v>
@@ -9202,10 +9316,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>37</v>
@@ -9220,7 +9334,7 @@
         <v>61</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>40</v>
@@ -9228,10 +9342,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>37</v>
@@ -9246,7 +9360,7 @@
         <v>61</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H72" s="5" t="s">
         <v>40</v>
@@ -9254,10 +9368,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>37</v>
@@ -9266,13 +9380,13 @@
         <v>37</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H73" s="5" t="s">
         <v>40</v>
@@ -9280,10 +9394,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>37</v>
@@ -9292,13 +9406,13 @@
         <v>37</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>407</v>
+        <v>365</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>40</v>
@@ -9306,10 +9420,10 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>37</v>
@@ -9318,13 +9432,13 @@
         <v>37</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>40</v>
@@ -9332,27 +9446,105 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C76" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D79" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E79" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F79" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="H76" s="5" t="s">
+      <c r="G79" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="H79" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -9365,7 +9557,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -10003,51 +10195,51 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>65</v>
+      <c r="D25" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>37</v>
+      <c r="D26" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>40</v>
@@ -10055,10 +10247,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>37</v>
@@ -10070,10 +10262,10 @@
         <v>9</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>40</v>
@@ -10081,10 +10273,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>37</v>
@@ -10096,10 +10288,10 @@
         <v>9</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>40</v>
@@ -10107,10 +10299,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>37</v>
@@ -10125,7 +10317,7 @@
         <v>38</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>40</v>
@@ -10133,36 +10325,36 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>37</v>
+      <c r="D30" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>37</v>
@@ -10171,13 +10363,13 @@
         <v>37</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>40</v>
@@ -10185,10 +10377,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>37</v>
@@ -10203,7 +10395,7 @@
         <v>52</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>40</v>
@@ -10211,10 +10403,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>37</v>
@@ -10226,10 +10418,10 @@
         <v>10</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>40</v>
@@ -10237,10 +10429,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>37</v>
@@ -10252,10 +10444,10 @@
         <v>10</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>40</v>
@@ -10263,10 +10455,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>37</v>
@@ -10281,7 +10473,7 @@
         <v>52</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>40</v>
@@ -10289,10 +10481,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>37</v>
@@ -10301,13 +10493,13 @@
         <v>37</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>40</v>
@@ -10315,10 +10507,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>37</v>
@@ -10330,10 +10522,10 @@
         <v>11</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>217</v>
+        <v>11</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>40</v>
@@ -10341,10 +10533,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>37</v>
@@ -10356,10 +10548,10 @@
         <v>11</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>40</v>
@@ -10367,10 +10559,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>37</v>
@@ -10393,10 +10585,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>37</v>
@@ -10408,10 +10600,10 @@
         <v>11</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>224</v>
+        <v>11</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>40</v>
@@ -10419,10 +10611,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>37</v>
@@ -10437,7 +10629,7 @@
         <v>52</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>40</v>
@@ -10445,10 +10637,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>37</v>
@@ -10457,13 +10649,13 @@
         <v>37</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>40</v>
@@ -10471,10 +10663,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>37</v>
@@ -10489,7 +10681,7 @@
         <v>52</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>40</v>
@@ -10497,10 +10689,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>37</v>
@@ -10515,7 +10707,7 @@
         <v>52</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>40</v>
@@ -10523,16 +10715,16 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>65</v>
+      <c r="D45" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>12</v>
@@ -10541,7 +10733,7 @@
         <v>52</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>40</v>
@@ -10549,25 +10741,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>37</v>
+      <c r="D46" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>40</v>
@@ -10575,10 +10767,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>37</v>
@@ -10590,10 +10782,10 @@
         <v>13</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>40</v>
@@ -10601,10 +10793,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>37</v>
@@ -10619,7 +10811,7 @@
         <v>61</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>248</v>
+        <v>19</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>40</v>
@@ -10627,25 +10819,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D49" s="7" t="s">
-        <v>65</v>
+      <c r="D49" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>40</v>
@@ -10653,25 +10845,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>37</v>
+      <c r="D50" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>40</v>
@@ -10679,10 +10871,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>37</v>
@@ -10697,7 +10889,7 @@
         <v>52</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>40</v>
@@ -10705,10 +10897,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>37</v>
@@ -10723,7 +10915,7 @@
         <v>52</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>161</v>
+        <v>270</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>40</v>
@@ -10731,16 +10923,16 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>65</v>
+      <c r="D53" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>14</v>
@@ -10749,7 +10941,7 @@
         <v>52</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>264</v>
+        <v>165</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>40</v>
@@ -10757,10 +10949,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>37</v>
@@ -10775,7 +10967,7 @@
         <v>52</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>40</v>
@@ -10783,10 +10975,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>37</v>
@@ -10801,7 +10993,7 @@
         <v>52</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>161</v>
+        <v>278</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>40</v>
@@ -10809,10 +11001,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>37</v>
@@ -10821,13 +11013,13 @@
         <v>65</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>296</v>
+        <v>52</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>297</v>
+        <v>165</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>40</v>
@@ -10835,10 +11027,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>37</v>
@@ -10850,10 +11042,10 @@
         <v>15</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>161</v>
+        <v>308</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>40</v>
@@ -10861,10 +11053,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>37</v>
@@ -10873,13 +11065,13 @@
         <v>65</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>52</v>
+        <v>307</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>308</v>
+        <v>165</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>40</v>
@@ -10887,10 +11079,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>37</v>
@@ -10905,7 +11097,7 @@
         <v>52</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>40</v>
@@ -10913,10 +11105,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>37</v>
@@ -10931,7 +11123,7 @@
         <v>52</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>40</v>
@@ -10939,10 +11131,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>37</v>
@@ -10954,10 +11146,10 @@
         <v>16</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>40</v>
@@ -10965,10 +11157,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>37</v>
@@ -10980,10 +11172,10 @@
         <v>16</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="H62" s="5" t="s">
         <v>40</v>
@@ -10991,25 +11183,25 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>37</v>
+      <c r="D63" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>40</v>
@@ -11017,10 +11209,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>37</v>
@@ -11035,7 +11227,7 @@
         <v>48</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>40</v>
@@ -11043,10 +11235,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>37</v>
@@ -11058,10 +11250,10 @@
         <v>17</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>40</v>
@@ -11069,10 +11261,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>37</v>
@@ -11087,7 +11279,7 @@
         <v>61</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>40</v>
@@ -11095,10 +11287,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>37</v>
@@ -11113,7 +11305,7 @@
         <v>61</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>40</v>
@@ -11121,10 +11313,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>37</v>
@@ -11139,7 +11331,7 @@
         <v>61</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>40</v>
@@ -11147,10 +11339,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>37</v>
@@ -11165,7 +11357,7 @@
         <v>61</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>161</v>
+        <v>349</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>40</v>
@@ -11173,10 +11365,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>37</v>
@@ -11188,10 +11380,10 @@
         <v>17</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>40</v>
@@ -11199,10 +11391,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>37</v>
@@ -11217,7 +11409,7 @@
         <v>52</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>345</v>
+        <v>165</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>40</v>
@@ -11225,10 +11417,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>37</v>
@@ -11243,7 +11435,7 @@
         <v>52</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="H72" s="5" t="s">
         <v>40</v>
@@ -11251,10 +11443,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>37</v>
@@ -11266,10 +11458,10 @@
         <v>17</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="H73" s="5" t="s">
         <v>40</v>
@@ -11277,10 +11469,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>37</v>
@@ -11295,7 +11487,7 @@
         <v>61</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>40</v>
@@ -11303,10 +11495,10 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>37</v>
@@ -11321,7 +11513,7 @@
         <v>61</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>40</v>
@@ -11329,10 +11521,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>37</v>
@@ -11347,7 +11539,7 @@
         <v>61</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="H76" s="5" t="s">
         <v>40</v>
@@ -11355,16 +11547,16 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>65</v>
+      <c r="D77" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>17</v>
@@ -11373,7 +11565,7 @@
         <v>61</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>40</v>
@@ -11381,10 +11573,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>37</v>
@@ -11393,13 +11585,13 @@
         <v>65</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="H78" s="5" t="s">
         <v>40</v>
@@ -11407,10 +11599,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>37</v>
@@ -11425,7 +11617,7 @@
         <v>61</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>161</v>
+        <v>376</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>40</v>
@@ -11433,10 +11625,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>37</v>
@@ -11448,10 +11640,10 @@
         <v>18</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>40</v>
@@ -11459,10 +11651,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>37</v>
@@ -11474,10 +11666,10 @@
         <v>18</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>373</v>
+        <v>165</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>40</v>
@@ -11485,10 +11677,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>37</v>
@@ -11500,10 +11692,10 @@
         <v>18</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>61</v>
+        <v>381</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>40</v>
@@ -11511,10 +11703,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>37</v>
@@ -11529,7 +11721,7 @@
         <v>61</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>40</v>
@@ -11537,10 +11729,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>37</v>
@@ -11555,7 +11747,7 @@
         <v>61</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>329</v>
+        <v>390</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>40</v>
@@ -11563,10 +11755,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>37</v>
@@ -11578,10 +11770,10 @@
         <v>18</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>40</v>
@@ -11589,10 +11781,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>37</v>
@@ -11604,10 +11796,10 @@
         <v>18</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>52</v>
+        <v>381</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>161</v>
+        <v>343</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>40</v>
@@ -11615,10 +11807,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>37</v>
@@ -11630,10 +11822,10 @@
         <v>18</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H87" s="5" t="s">
         <v>40</v>
@@ -11641,25 +11833,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D88" s="6" t="s">
-        <v>37</v>
+      <c r="D88" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>390</v>
+        <v>165</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>40</v>
@@ -11667,10 +11859,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>37</v>
@@ -11685,7 +11877,7 @@
         <v>61</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="H89" s="5" t="s">
         <v>40</v>
@@ -11693,10 +11885,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>37</v>
@@ -11711,7 +11903,7 @@
         <v>61</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="H90" s="5" t="s">
         <v>40</v>
@@ -11719,10 +11911,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>37</v>
@@ -11737,7 +11929,7 @@
         <v>61</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H91" s="5" t="s">
         <v>40</v>
@@ -11745,10 +11937,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>37</v>
@@ -11760,10 +11952,10 @@
         <v>19</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>212</v>
+        <v>407</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>40</v>
@@ -11771,10 +11963,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>37</v>
@@ -11789,7 +11981,7 @@
         <v>61</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>403</v>
+        <v>365</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>40</v>
@@ -11797,10 +11989,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>37</v>
@@ -11809,13 +12001,13 @@
         <v>37</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>40</v>
@@ -11823,10 +12015,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>37</v>
@@ -11838,10 +12030,10 @@
         <v>20</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>40</v>
@@ -11849,10 +12041,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>37</v>
@@ -11864,10 +12056,10 @@
         <v>20</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>48</v>
+        <v>381</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>40</v>
@@ -11875,10 +12067,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>37</v>
@@ -11890,10 +12082,10 @@
         <v>20</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>161</v>
+        <v>422</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>40</v>
@@ -11901,10 +12093,10 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>37</v>
@@ -11913,13 +12105,13 @@
         <v>37</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>419</v>
+        <v>165</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>40</v>
@@ -11927,42 +12119,42 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="8" t="s">
-        <v>422</v>
+      <c r="D99" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>424</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>422</v>
+        <v>187</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>22</v>
@@ -11971,44 +12163,44 @@
         <v>52</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D101" s="6" t="s">
-        <v>37</v>
+      <c r="D101" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>52</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>40</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>37</v>
@@ -12023,7 +12215,7 @@
         <v>52</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="H102" s="5" t="s">
         <v>40</v>
@@ -12031,10 +12223,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>37</v>
@@ -12049,7 +12241,7 @@
         <v>52</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>40</v>
@@ -12057,10 +12249,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>37</v>
@@ -12075,7 +12267,7 @@
         <v>52</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="H104" s="5" t="s">
         <v>40</v>
@@ -12083,10 +12275,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>37</v>
@@ -12101,7 +12293,7 @@
         <v>52</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>40</v>
@@ -12109,16 +12301,16 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D106" s="7" t="s">
-        <v>65</v>
+      <c r="D106" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>23</v>
@@ -12127,7 +12319,7 @@
         <v>52</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>161</v>
+        <v>452</v>
       </c>
       <c r="H106" s="5" t="s">
         <v>40</v>
@@ -12135,25 +12327,25 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>65</v>
+        <v>454</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="H107" s="5" t="s">
         <v>40</v>
@@ -12161,10 +12353,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>65</v>
@@ -12179,7 +12371,7 @@
         <v>52</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>40</v>
@@ -12187,10 +12379,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>65</v>
@@ -12202,10 +12394,10 @@
         <v>24</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>40</v>
@@ -12213,10 +12405,10 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>65</v>
@@ -12231,9 +12423,61 @@
         <v>52</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>458</v>
+        <v>165</v>
       </c>
       <c r="H110" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H112" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -12416,10 +12660,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>37</v>
@@ -12431,10 +12675,10 @@
         <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>40</v>
@@ -12442,10 +12686,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>37</v>
@@ -12460,7 +12704,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>40</v>
@@ -12468,16 +12712,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>37</v>
+      <c r="D9" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>9</v>
@@ -12486,18 +12730,18 @@
         <v>38</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>37</v>
@@ -12509,10 +12753,10 @@
         <v>15</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>40</v>
@@ -12520,10 +12764,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>37</v>
@@ -12535,10 +12779,10 @@
         <v>15</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>40</v>
@@ -12546,10 +12790,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>37</v>
@@ -12561,10 +12805,10 @@
         <v>15</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>40</v>
@@ -12572,10 +12816,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>37</v>
@@ -12587,10 +12831,10 @@
         <v>15</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>40</v>
@@ -12598,10 +12842,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>37</v>
@@ -12613,10 +12857,10 @@
         <v>15</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>40</v>
@@ -12624,10 +12868,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>37</v>
@@ -12639,10 +12883,10 @@
         <v>15</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>40</v>
@@ -12650,10 +12894,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>37</v>
@@ -12665,10 +12909,10 @@
         <v>15</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>40</v>
@@ -12676,10 +12920,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>37</v>
@@ -12691,10 +12935,10 @@
         <v>15</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>40</v>
@@ -12702,10 +12946,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>37</v>
@@ -12717,10 +12961,10 @@
         <v>15</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>40</v>
@@ -12728,10 +12972,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>37</v>
@@ -12743,10 +12987,10 @@
         <v>15</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>40</v>
@@ -12754,10 +12998,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>37</v>
@@ -12769,10 +13013,10 @@
         <v>15</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>40</v>
@@ -12780,10 +13024,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>37</v>
@@ -12795,10 +13039,10 @@
         <v>15</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>40</v>
@@ -12806,10 +13050,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>37</v>
@@ -12821,7 +13065,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>50</v>
@@ -12832,10 +13076,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>37</v>
@@ -12850,7 +13094,7 @@
         <v>66</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>40</v>
@@ -12858,10 +13102,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>65</v>
@@ -12876,7 +13120,7 @@
         <v>66</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>40</v>
@@ -12884,10 +13128,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>65</v>
@@ -12899,10 +13143,10 @@
         <v>24</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>40</v>
@@ -12928,41 +13172,41 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>40</v>
@@ -12970,13 +13214,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>40</v>
@@ -12984,97 +13228,97 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>40</v>
@@ -13082,27 +13326,27 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>40</v>
@@ -13110,58 +13354,58 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
